--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-07-2025.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_23-07-2025.xlsx
@@ -589,29 +589,29 @@
       <c r="M2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -627,7 +627,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>£16.68</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/25mm_celotex_tb4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -710,29 +710,29 @@
       <c r="M3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -748,7 +748,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>£19.42</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/30mm_celotex_tb4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -831,29 +831,29 @@
       <c r="M4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -869,7 +869,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>£22.68</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/40mm_celotex_tb4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -952,29 +952,29 @@
       <c r="M5" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -990,7 +990,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>£21.93</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/50mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1073,29 +1073,29 @@
       <c r="M6" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>£29.50</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/60mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1194,29 +1194,29 @@
       <c r="M7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>£34.85</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/70mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1315,29 +1315,29 @@
       <c r="M8" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>£34.66</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/75mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1436,29 +1436,29 @@
       <c r="M9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>£38.36</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/80mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1557,29 +1557,29 @@
       <c r="M10" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>£41.16</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/90mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1678,29 +1678,29 @@
       <c r="M11" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>£38.47</t>
+          <t>Error: 500 Server Error: Internal Server Error for url: https://www.insulationshop.co/100mm_celotex_ga4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1799,29 +1799,29 @@
       <c r="M12" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1837,7 +1837,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>£50.96</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/110mm_celotex_xr4000_pir_insulation.html?search=XR4110</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1920,29 +1920,29 @@
       <c r="M13" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>£51.70</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/120mm_celotex_xr4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -2041,29 +2041,29 @@
       <c r="M14" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>£61.93</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/130mm_celotex_gxr4000_pir_insulation.html?search=XR4130</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -2162,29 +2162,29 @@
       <c r="M15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>£65.16</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/140mm_celotex_xr4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2283,29 +2283,29 @@
       <c r="M16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2321,7 +2321,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>£74.88</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/150mm_celotex_gxr4000_pir_insulation.html</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2418,7 +2418,7 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>£959.7</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/165mm_celotex_xr4000.html</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2501,29 +2501,29 @@
       <c r="M18" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>£1164.06</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/200mm_celotex_xr4000.html</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2622,29 +2622,29 @@
       <c r="M19" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2660,7 +2660,7 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>£48.24</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/25mm_celotex_pl4000_rigid_pir_insulation_bonded_to_plasterboard.html</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -2743,29 +2743,29 @@
       <c r="M20" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>£58.53</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/40mm_celotex_pl4000_rigid_pir_insulation_bonded_to_plasterboard.html</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2864,29 +2864,29 @@
       <c r="M21" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>£66.08</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/50mm_celotex_pl4000_rigid_pir_insulation_bonded_to_plasterboard.html</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2985,29 +2985,29 @@
       <c r="M22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -3023,7 +3023,7 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>£68.87</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/60mm_celotex_pl4000_rigid_pir_insulation_bonded_to_plasterboard.html</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
@@ -3106,29 +3106,29 @@
       <c r="M23" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>£65.48</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/50mm_celotex_cw4000_rigid_pir_cavity_insulation.html</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3227,29 +3227,29 @@
       <c r="M24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -3265,7 +3265,7 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>£63.59</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/75mm_celotex_cw4000_rigid_pir_cavity_insulation.html</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
@@ -3348,29 +3348,29 @@
       <c r="M25" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>£1439.04</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/85mm_celotex_cw4000_rigid_pir_cavity_insulation.html</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3469,29 +3469,29 @@
       <c r="M26" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="attribute1999"]"}
-  (Session info: chrome=138.0.7204.97); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
+  (Session info: chrome=138.0.7204.158); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#no-such-element-exception
 Stacktrace:
-	GetHandleVerifier [0x0x7ff6d5f9e935+77845]
-	GetHandleVerifier [0x0x7ff6d5f9e990+77936]
-	(No symbol) [0x0x7ff6d5d59cda]
-	(No symbol) [0x0x7ff6d5db06aa]
-	(No symbol) [0x0x7ff6d5db095c]
-	(No symbol) [0x0x7ff6d5e03d07]
-	(No symbol) [0x0x7ff6d5dd890f]
-	(No symbol) [0x0x7ff6d5e00b07]
-	(No symbol) [0x0x7ff6d5dd86a3]
-	(No symbol) [0x0x7ff6d5da1791]
-	(No symbol) [0x0x7ff6d5da2523]
-	GetHandleVerifier [0x0x7ff6d627684d+3059501]
-	GetHandleVerifier [0x0x7ff6d6270c0d+3035885]
-	GetHandleVerifier [0x0x7ff6d6290400+3164896]
-	GetHandleVerifier [0x0x7ff6d5fb8c3e+185118]
-	GetHandleVerifier [0x0x7ff6d5fc054f+216111]
-	GetHandleVerifier [0x0x7ff6d5fa72e4+113092]
-	GetHandleVerifier [0x0x7ff6d5fa7499+113529]
-	GetHandleVerifier [0x0x7ff6d5f8e298+10616]
-	BaseThreadInitThunk [0x0x7ffb00c3e8d7+23]
-	RtlUserThreadStart [0x0x7ffb02a5c34c+44]
+	GetHandleVerifier [0x0x7ff72b33e935+77845]
+	GetHandleVerifier [0x0x7ff72b33e990+77936]
+	(No symbol) [0x0x7ff72b0f9cda]
+	(No symbol) [0x0x7ff72b1506aa]
+	(No symbol) [0x0x7ff72b15095c]
+	(No symbol) [0x0x7ff72b1a3d07]
+	(No symbol) [0x0x7ff72b17890f]
+	(No symbol) [0x0x7ff72b1a0b07]
+	(No symbol) [0x0x7ff72b1786a3]
+	(No symbol) [0x0x7ff72b141791]
+	(No symbol) [0x0x7ff72b142523]
+	GetHandleVerifier [0x0x7ff72b61684d+3059501]
+	GetHandleVerifier [0x0x7ff72b610c0d+3035885]
+	GetHandleVerifier [0x0x7ff72b630400+3164896]
+	GetHandleVerifier [0x0x7ff72b358c3e+185118]
+	GetHandleVerifier [0x0x7ff72b36054f+216111]
+	GetHandleVerifier [0x0x7ff72b3472e4+113092]
+	GetHandleVerifier [0x0x7ff72b347499+113529]
+	GetHandleVerifier [0x0x7ff72b32e298+10616]
+	BaseThreadInitThunk [0x0x7ffb1377e8d7+23]
+	RtlUserThreadStart [0x0x7ffb157fc34c+44]
 </t>
         </is>
       </c>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>£62.02</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/100mm_celotex_cw4000_rigid_pir_cavity_insulation.html</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>£1588.8</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/90mm_celotex_thermaclass_cavity_wall_21.html</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>£1700.0</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/115mm_celotex_thermaclass_cavity_wall_21.html</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>£1804.16</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.insulationshop.co/140mm_celotex_thermaclass_cavity_wall_21.html</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
